--- a/site/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,6 +438,402 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>h_01JZW9E9B6ZZRTWQSYHXT2DAAF</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01JZW9E9B6ZZRTWQSYHXT2DAAF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Key Functions</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>h_01K06FVR3HAYYM66WATF77B0B4</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01K06FVR3HAYYM66WATF77B0B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Prerequisites</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>h_01JZW70JA70W2SCAXXM5NFYAK0</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01JZW70JA70W2SCAXXM5NFYAK0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Integration Setup</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>h_01F6EH0W486EMXD6A000X2Z4YZ</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01F6EH0W486EMXD6A000X2Z4YZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Create Integration</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Configuration</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Applications</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Parameters</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Log Settings</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Notification Settings</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Notification Settings</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>01KFD1AMVYPNY4PY2ZB7A64VGC</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#01KFD1AMVYPNY4PY2ZB7A64VGC</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Notification Report Settings</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Report Settings</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Log Insight Settings</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Attribute Map</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -617,73 +617,73 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Integration Scenarios</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
+          <t>h_01K04AVZNHW4RD086HGMDCJSM6</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01K04AVZNHW4RD086HGMDCJSM6</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>General Settings</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>01KF2RH05MP5RR93W69VEMT2AR</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#01KF2RH05MP5RR93W69VEMT2AR</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Onboarding Ticket</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>01KFD1AMVYPNY4PY2ZB7A64VGC</t>
+          <t>01KFD0RVZ9EM5G97GM5P4XPJHZ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#01KFD1AMVYPNY4PY2ZB7A64VGC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#01KFD0RVZ9EM5G97GM5P4XPJHZ</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Onboarding User Configuration</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -693,41 +693,41 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+          <t>h_01KMCMTH5PJE4M1H4BQSJW767W</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01KMCMTH5PJE4M1H4BQSJW767W</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Onboarding Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>h_01KMCSRCV2JZP9KW9BQ1BQV4A5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01KMCSRCV2JZP9KW9BQ1BQV4A5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Mover Ticket</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,98 +737,252 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>h_01KMCSRCV2GQ5JYH11NK970FTV</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01KMCSRCV2GQ5JYH11NK970FTV</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Mover User Configuration</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>h_01KMCSRCV2HD2BQAX8QCC7RQ0D</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01KMCSRCV2HD2BQAX8QCC7RQ0D</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Notification Settings</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>01KFD1AMVYPNY4PY2ZB7A64VGC</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#01KFD1AMVYPNY4PY2ZB7A64VGC</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Notification Report Settings</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Report Settings</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Log Insight Settings</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Attribute Map</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -715,12 +715,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KMCSRCV2JZP9KW9BQ1BQV4A5</t>
+          <t>h_01KMD17T1BCVPJFDRCXN2QCR7B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01KMCSRCV2JZP9KW9BQ1BQV4A5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01KMD17T1BCVPJFDRCXN2QCR7B</t>
         </is>
       </c>
     </row>
@@ -737,12 +737,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KMCSRCV2GQ5JYH11NK970FTV</t>
+          <t>h_01KMD17T1B3SVJ1K4Z698Y3VKK</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01KMCSRCV2GQ5JYH11NK970FTV</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01KMD17T1B3SVJ1K4Z698Y3VKK</t>
         </is>
       </c>
     </row>
@@ -759,41 +759,41 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KMCSRCV2HD2BQAX8QCC7RQ0D</t>
+          <t>h_01KMD17T1BC4B1D81KF66B0QY0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01KMCSRCV2HD2BQAX8QCC7RQ0D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01KMD17T1BC4B1D81KF66B0QY0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Mover Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
+          <t>h_01KMD17T1BYNH90EBVZWCTTSTG</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01KMD17T1BYNH90EBVZWCTTSTG</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Offboarding Ticket</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>h_01KMD17T1BAHTAWWK13CX1MN1N</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01KMD17T1BAHTAWWK13CX1MN1N</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Offboarding User Configuration</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,19 +825,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>01KFD1AMVYPNY4PY2ZB7A64VGC</t>
+          <t>h_01KMD17T1BVJ0DGPHCV9TXN0YB</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#01KFD1AMVYPNY4PY2ZB7A64VGC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01KMD17T1BVJ0DGPHCV9TXN0YB</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Offboarding Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,19 +847,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+          <t>h_01KMD17T1BGAQN0362C290M487</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01KMD17T1BGAQN0362C290M487</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>h_01KMD17T1BZ3DGFX84ZY0GFBJJ</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01KMD17T1BZ3DGFX84ZY0GFBJJ</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,98 +891,186 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>01KFD1AMVYPNY4PY2ZB7A64VGC</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#01KFD1AMVYPNY4PY2ZB7A64VGC</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>01K5X7TJQR0KMMYYXZF7N7W9SG</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#01K5X7TJQR0KMMYYXZF7N7W9SG</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Log Insight Settings</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Attribute Map</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -715,12 +715,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KMD17T1BCVPJFDRCXN2QCR7B</t>
+          <t>h_01KMD5AWFHH5TC3F48TD005C3W</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01KMD17T1BCVPJFDRCXN2QCR7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01KMD5AWFHH5TC3F48TD005C3W</t>
         </is>
       </c>
     </row>
@@ -737,12 +737,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KMD17T1B3SVJ1K4Z698Y3VKK</t>
+          <t>h_01KMD5AWFJ1P5BAMBZAS03KCYD</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01KMD17T1B3SVJ1K4Z698Y3VKK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01KMD5AWFJ1P5BAMBZAS03KCYD</t>
         </is>
       </c>
     </row>
@@ -759,19 +759,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KMD17T1BC4B1D81KF66B0QY0</t>
+          <t>h_01KMD5AWFJ9MCCTTNPTPNG0MFJ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01KMD17T1BC4B1D81KF66B0QY0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01KMD5AWFJ9MCCTTNPTPNG0MFJ</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mover Settings</t>
+          <t>Mover Tickets</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KMD17T1BYNH90EBVZWCTTSTG</t>
+          <t>h_01KMD5AWFJE500CFVK8FX1N1RJ</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01KMD17T1BYNH90EBVZWCTTSTG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01KMD5AWFJE500CFVK8FX1N1RJ</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KMD17T1BAHTAWWK13CX1MN1N</t>
+          <t>h_01KMD5AWFJH53HVKXHWM6M2XGC</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01KMD17T1BAHTAWWK13CX1MN1N</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01KMD5AWFJH53HVKXHWM6M2XGC</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KMD17T1BVJ0DGPHCV9TXN0YB</t>
+          <t>h_01KMD5AWFJRX9PVK4ANRJBJVRA</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01KMD17T1BVJ0DGPHCV9TXN0YB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01KMD5AWFJRX9PVK4ANRJBJVRA</t>
         </is>
       </c>
     </row>
@@ -847,19 +847,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KMD17T1BGAQN0362C290M487</t>
+          <t>h_01KMD5AWFJNQ38H3KWJ05KDK4J</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01KMD17T1BGAQN0362C290M487</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01KMD5AWFJNQ38H3KWJ05KDK4J</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Transfer Ticket</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,41 +869,41 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KMD17T1BZ3DGFX84ZY0GFBJJ</t>
+          <t>h_01KMD5AWFJYKR7X4Q36ARN8Y4K</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01KMD17T1BZ3DGFX84ZY0GFBJJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01KMD5AWFJYKR7X4Q36ARN8Y4K</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Transfer User Configuration</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>h_01KMD5AWFJTRTXW0QA8WP2272J</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01KMD5AWFJTRTXW0QA8WP2272J</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Transfer Tickets</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,41 +913,41 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>01KFD1AMVYPNY4PY2ZB7A64VGC</t>
+          <t>h_01KMD5AWFJPQCFK8JRSX4CVH28</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#01KFD1AMVYPNY4PY2ZB7A64VGC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01KMD5AWFJPQCFK8JRSX4CVH28</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+          <t>h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,120 +957,186 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>01KFD1AMVYPNY4PY2ZB7A64VGC</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#01KFD1AMVYPNY4PY2ZB7A64VGC</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>01K5X7TJQR0KMMYYXZF7N7W9SG</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#01K5X7TJQR0KMMYYXZF7N7W9SG</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Log Insight Settings</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Attribute Map</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloITSM-Ticket-Management-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
